--- a/data/trans_orig/IQ2601_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IQ2601_R-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>35346</t>
+          <t>36405</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>51268</t>
+          <t>50909</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>39,75%</t>
+          <t>40,94%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>57,65%</t>
+          <t>57,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>34168</t>
+          <t>34239</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>49445</t>
+          <t>48986</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>40,55%</t>
+          <t>40,63%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>58,68%</t>
+          <t>58,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>75135</t>
+          <t>75505</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>96033</t>
+          <t>95972</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>43,38%</t>
+          <t>43,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>55,45%</t>
+          <t>55,41%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12554</t>
+          <t>12129</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>24218</t>
+          <t>24453</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8597</t>
+          <t>8040</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19171</t>
+          <t>19073</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>23145</t>
+          <t>23665</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>39760</t>
+          <t>40906</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>23,62%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10102</t>
+          <t>9736</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>21263</t>
+          <t>21216</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>10428</t>
+          <t>10890</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>22500</t>
+          <t>22456</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>26,65%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>24192</t>
+          <t>24035</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>40863</t>
+          <t>39759</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>22,96%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1385</t>
+          <t>1357</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7868</t>
+          <t>8278</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1292</t>
+          <t>1296</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7273</t>
+          <t>7297</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3371</t>
+          <t>3483</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12299</t>
+          <t>11835</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>6,83%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5325</t>
+          <t>5623</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>14713</t>
+          <t>14918</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>5896</t>
+          <t>5870</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>15366</t>
+          <t>15145</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>13568</t>
+          <t>13256</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>26315</t>
+          <t>26653</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,39%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>144090</t>
+          <t>145814</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>175505</t>
+          <t>177739</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>35,45%</t>
+          <t>35,88%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>43,18%</t>
+          <t>43,73%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>180827</t>
+          <t>181323</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>214691</t>
+          <t>213310</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>38,58%</t>
+          <t>38,68%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>45,8%</t>
+          <t>45,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>335284</t>
+          <t>334506</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>383003</t>
+          <t>383833</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>38,31%</t>
+          <t>38,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>43,76%</t>
+          <t>43,86%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>91855</t>
+          <t>92942</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>121302</t>
+          <t>120924</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>29,75%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>84588</t>
+          <t>83799</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>111623</t>
+          <t>112661</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>185204</t>
+          <t>184997</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>225360</t>
+          <t>225195</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>25,73%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>81975</t>
+          <t>81865</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>109603</t>
+          <t>109408</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>26,92%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>95010</t>
+          <t>95089</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>123244</t>
+          <t>124900</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>26,65%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>185672</t>
+          <t>185865</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>224619</t>
+          <t>225616</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>25,78%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10647</t>
+          <t>10085</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>23804</t>
+          <t>22917</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13528</t>
+          <t>14009</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>26848</t>
+          <t>28618</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>27155</t>
+          <t>26465</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>45932</t>
+          <t>46421</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,3%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>20459</t>
+          <t>20056</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>36726</t>
+          <t>36275</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>33573</t>
+          <t>34228</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>53767</t>
+          <t>54164</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>58774</t>
+          <t>58673</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>83714</t>
+          <t>83596</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,55%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>67824</t>
+          <t>67925</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>89507</t>
+          <t>89086</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>40,06%</t>
+          <t>40,12%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>52,86%</t>
+          <t>52,61%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>66093</t>
+          <t>66351</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>86219</t>
+          <t>86987</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>43,05%</t>
+          <t>43,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>56,16%</t>
+          <t>56,66%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>139823</t>
+          <t>139931</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>169287</t>
+          <t>170029</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>43,31%</t>
+          <t>43,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>52,44%</t>
+          <t>52,67%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>35750</t>
+          <t>34715</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>53741</t>
+          <t>53826</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>31,79%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>26977</t>
+          <t>26386</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>43292</t>
+          <t>43204</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>28,14%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>66980</t>
+          <t>67249</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>91972</t>
+          <t>90733</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>28,1%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>27900</t>
+          <t>27870</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>45265</t>
+          <t>44833</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>26,48%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>20367</t>
+          <t>20526</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>35944</t>
+          <t>35991</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>52326</t>
+          <t>52223</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>74853</t>
+          <t>74908</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>23,2%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1401</t>
+          <t>1567</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8548</t>
+          <t>9172</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2748</t>
+          <t>2767</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10720</t>
+          <t>10876</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6024</t>
+          <t>5951</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>16582</t>
+          <t>16274</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,04%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3226</t>
+          <t>2929</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>11469</t>
+          <t>11561</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>5886</t>
+          <t>5823</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>16206</t>
+          <t>15426</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>10111</t>
+          <t>10772</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>23195</t>
+          <t>23313</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,22%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>261211</t>
+          <t>263129</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>302808</t>
+          <t>303026</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>39,3%</t>
+          <t>39,59%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>45,56%</t>
+          <t>45,59%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>295263</t>
+          <t>292427</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>336150</t>
+          <t>336523</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>41,79%</t>
+          <t>41,39%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>47,58%</t>
+          <t>47,63%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>569370</t>
+          <t>567711</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>629991</t>
+          <t>626125</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>41,52%</t>
+          <t>41,4%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>45,94%</t>
+          <t>45,66%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>151083</t>
+          <t>150806</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>187087</t>
+          <t>186388</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>22,69%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>128203</t>
+          <t>130456</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>162123</t>
+          <t>166954</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>23,63%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>287379</t>
+          <t>289072</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>338194</t>
+          <t>340597</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>24,84%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>130364</t>
+          <t>130200</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>165276</t>
+          <t>163718</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>135120</t>
+          <t>136404</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>171193</t>
+          <t>170633</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>274959</t>
+          <t>274371</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>323970</t>
+          <t>322577</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>23,53%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>17118</t>
+          <t>16961</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>32421</t>
+          <t>32215</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>21029</t>
+          <t>22360</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>38254</t>
+          <t>39061</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>42122</t>
+          <t>42082</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>64777</t>
+          <t>65613</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3208,7 +3208,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,79%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>33642</t>
+          <t>33955</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>53420</t>
+          <t>54928</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>51938</t>
+          <t>51060</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>75888</t>
+          <t>74815</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>91310</t>
+          <t>90109</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>122277</t>
+          <t>121673</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,87%</t>
         </is>
       </c>
     </row>
@@ -3692,12 +3692,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>22900</t>
+          <t>22360</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>38272</t>
+          <t>37160</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>42,47%</t>
+          <t>41,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18319</t>
+          <t>17980</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>33021</t>
+          <t>31889</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>38,59%</t>
+          <t>37,27%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>44940</t>
+          <t>45598</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>65156</t>
+          <t>64984</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>37,09%</t>
+          <t>36,99%</t>
         </is>
       </c>
     </row>
@@ -3805,12 +3805,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7006</t>
+          <t>7206</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17056</t>
+          <t>17256</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3820,12 +3820,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5563</t>
+          <t>5323</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15411</t>
+          <t>15203</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3855,12 +3855,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>14138</t>
+          <t>14745</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>29059</t>
+          <t>28622</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3890,12 +3890,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,29%</t>
         </is>
       </c>
     </row>
@@ -3918,12 +3918,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13841</t>
+          <t>14288</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>27258</t>
+          <t>27907</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3933,12 +3933,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>30,97%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3953,12 +3953,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>14539</t>
+          <t>13675</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>27232</t>
+          <t>27112</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3968,12 +3968,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>31,83%</t>
+          <t>31,69%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>31770</t>
+          <t>31040</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>50533</t>
+          <t>49719</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4003,12 +4003,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>28,3%</t>
         </is>
       </c>
     </row>
@@ -4031,12 +4031,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7314</t>
+          <t>7043</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17750</t>
+          <t>17593</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4046,12 +4046,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7166</t>
+          <t>7413</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18948</t>
+          <t>19339</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4081,12 +4081,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>16761</t>
+          <t>16988</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>32899</t>
+          <t>32253</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4116,12 +4116,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,36%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>11862</t>
+          <t>11955</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>23742</t>
+          <t>23356</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>25,92%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>13625</t>
+          <t>13498</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>26788</t>
+          <t>27085</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>31,31%</t>
+          <t>31,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>28016</t>
+          <t>28529</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>45889</t>
+          <t>45049</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>25,64%</t>
         </is>
       </c>
     </row>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>113724</t>
+          <t>113885</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>143638</t>
+          <t>147458</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>32,79%</t>
+          <t>33,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>119545</t>
+          <t>119143</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>152350</t>
+          <t>150822</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>31,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>242119</t>
+          <t>239665</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>286082</t>
+          <t>285751</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>26,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>31,25%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>78685</t>
+          <t>77837</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>104785</t>
+          <t>105935</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>86563</t>
+          <t>84987</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>115121</t>
+          <t>113592</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>171492</t>
+          <t>169502</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>211564</t>
+          <t>209458</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>22,9%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>85741</t>
+          <t>84181</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>113933</t>
+          <t>113955</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4615,7 +4615,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>85354</t>
+          <t>87149</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>115003</t>
+          <t>117557</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>179854</t>
+          <t>178471</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>222682</t>
+          <t>224093</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>24,5%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15556</t>
+          <t>14445</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>30487</t>
+          <t>30388</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>29613</t>
+          <t>28959</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>49628</t>
+          <t>48928</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>49050</t>
+          <t>48680</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>73898</t>
+          <t>74226</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,12%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>82654</t>
+          <t>83403</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>111070</t>
+          <t>112922</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>25,78%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>88420</t>
+          <t>88372</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>118577</t>
+          <t>118290</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>24,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>180038</t>
+          <t>179454</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>219963</t>
+          <t>220899</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>24,16%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>50216</t>
+          <t>50951</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>70726</t>
+          <t>71592</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>31,92%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>44,31%</t>
+          <t>44,85%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>38672</t>
+          <t>38993</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>58294</t>
+          <t>59355</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,67%</t>
+          <t>36,32%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>93911</t>
+          <t>94724</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>121336</t>
+          <t>122199</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>37,56%</t>
+          <t>37,83%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>30907</t>
+          <t>30045</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>49694</t>
+          <t>49486</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>31090</t>
+          <t>30956</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>49206</t>
+          <t>49575</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,11%</t>
+          <t>30,33%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>67082</t>
+          <t>67384</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>92550</t>
+          <t>92878</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>28,75%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>18036</t>
+          <t>18624</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>34335</t>
+          <t>33943</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>27779</t>
+          <t>27440</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>44957</t>
+          <t>45204</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>27,66%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>50294</t>
+          <t>51019</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>74771</t>
+          <t>73954</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>22,89%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2155</t>
+          <t>2140</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9727</t>
+          <t>9444</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5211</t>
+          <t>5206</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>15160</t>
+          <t>15874</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5450,7 +5450,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>9071</t>
+          <t>8603</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>21315</t>
+          <t>20930</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,48%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>21571</t>
+          <t>21070</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>36808</t>
+          <t>37503</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>23560</t>
+          <t>23972</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>39930</t>
+          <t>40170</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>49143</t>
+          <t>49611</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>71776</t>
+          <t>72546</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>22,46%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>198018</t>
+          <t>198657</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>239767</t>
+          <t>238785</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>28,88%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>34,86%</t>
+          <t>34,72%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>187941</t>
+          <t>189410</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>229177</t>
+          <t>230715</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>26,11%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>31,59%</t>
+          <t>31,8%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>396490</t>
+          <t>399649</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>454700</t>
+          <t>457405</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>32,37%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>124126</t>
+          <t>125279</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>160064</t>
+          <t>158175</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>131481</t>
+          <t>131521</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>167621</t>
+          <t>166847</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>264175</t>
+          <t>267227</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>317145</t>
+          <t>315384</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>22,32%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>128697</t>
+          <t>128096</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>162517</t>
+          <t>163941</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>139797</t>
+          <t>138409</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>174469</t>
+          <t>175343</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>24,17%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>277139</t>
+          <t>278514</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>326300</t>
+          <t>328048</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>23,21%</t>
         </is>
       </c>
     </row>
@@ -6082,7 +6082,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>49345</t>
+          <t>49115</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>48355</t>
+          <t>48154</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>74943</t>
+          <t>73077</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>83825</t>
+          <t>83567</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>114229</t>
+          <t>114524</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,1%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>127810</t>
+          <t>125313</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>160980</t>
+          <t>161043</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6205,7 +6205,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>135695</t>
+          <t>135741</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>170335</t>
+          <t>170911</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>271663</t>
+          <t>271567</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>324526</t>
+          <t>322718</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6280,7 +6280,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>22,84%</t>
         </is>
       </c>
     </row>
@@ -6651,12 +6651,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15288</t>
+          <t>15712</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26852</t>
+          <t>27198</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6666,12 +6666,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>45,66%</t>
+          <t>46,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6686,12 +6686,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12424</t>
+          <t>12636</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24695</t>
+          <t>25220</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6701,12 +6701,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>35,99%</t>
+          <t>36,76%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6721,12 +6721,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>31240</t>
+          <t>31032</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>48732</t>
+          <t>47817</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>37,53%</t>
         </is>
       </c>
     </row>
@@ -6764,12 +6764,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12026</t>
+          <t>12079</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23965</t>
+          <t>24174</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6779,12 +6779,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>40,75%</t>
+          <t>41,11%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6799,12 +6799,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18410</t>
+          <t>18400</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>31937</t>
+          <t>31681</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6814,12 +6814,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>26,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>46,55%</t>
+          <t>46,17%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>33576</t>
+          <t>33808</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>50843</t>
+          <t>51147</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>39,9%</t>
+          <t>40,14%</t>
         </is>
       </c>
     </row>
@@ -6877,12 +6877,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1909</t>
+          <t>1527</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8821</t>
+          <t>8712</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6892,12 +6892,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3847</t>
+          <t>3681</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>12593</t>
+          <t>11743</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>6878</t>
+          <t>7045</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>17694</t>
+          <t>18549</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>14,56%</t>
         </is>
       </c>
     </row>
@@ -6990,12 +6990,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>547</t>
+          <t>544</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5360</t>
+          <t>5418</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7010,7 +7010,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7025,12 +7025,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2861</t>
+          <t>2704</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11231</t>
+          <t>11275</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7040,12 +7040,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7060,12 +7060,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4164</t>
+          <t>4117</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13395</t>
+          <t>13222</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7075,12 +7075,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,38%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>9489</t>
+          <t>8646</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>20482</t>
+          <t>19867</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>34,83%</t>
+          <t>33,78%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>8019</t>
+          <t>8114</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>19117</t>
+          <t>18987</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>27,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>19829</t>
+          <t>19913</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>35654</t>
+          <t>34855</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>27,35%</t>
         </is>
       </c>
     </row>
@@ -7333,12 +7333,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>122047</t>
+          <t>123970</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>154774</t>
+          <t>154957</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7348,12 +7348,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>26,61%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>33,22%</t>
+          <t>33,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7368,12 +7368,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>134194</t>
+          <t>135626</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>169115</t>
+          <t>168195</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7383,12 +7383,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,76%</t>
+          <t>34,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7403,12 +7403,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>269192</t>
+          <t>269124</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>314967</t>
+          <t>310717</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7418,12 +7418,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>28,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,07%</t>
+          <t>32,63%</t>
         </is>
       </c>
     </row>
@@ -7446,12 +7446,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>147569</t>
+          <t>148269</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>182577</t>
+          <t>180250</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>31,68%</t>
+          <t>31,83%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>39,19%</t>
+          <t>38,69%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7481,12 +7481,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>149041</t>
+          <t>147925</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>182620</t>
+          <t>183074</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7496,12 +7496,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>37,54%</t>
+          <t>37,63%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7516,12 +7516,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>303978</t>
+          <t>304537</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>352144</t>
+          <t>353966</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7531,12 +7531,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>31,98%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>36,98%</t>
+          <t>37,17%</t>
         </is>
       </c>
     </row>
@@ -7559,12 +7559,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>36461</t>
+          <t>35064</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>58281</t>
+          <t>56659</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7574,12 +7574,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>43600</t>
+          <t>42681</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>65347</t>
+          <t>66789</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7629,12 +7629,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>84298</t>
+          <t>84252</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>115362</t>
+          <t>117309</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7649,7 +7649,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,32%</t>
         </is>
       </c>
     </row>
@@ -7672,12 +7672,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8804</t>
+          <t>9212</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20717</t>
+          <t>21305</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7687,12 +7687,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7707,12 +7707,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12323</t>
+          <t>11601</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>26565</t>
+          <t>25742</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7722,12 +7722,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7742,12 +7742,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>24408</t>
+          <t>24511</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>43441</t>
+          <t>42716</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,49%</t>
         </is>
       </c>
     </row>
@@ -7785,12 +7785,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>91285</t>
+          <t>89519</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>119791</t>
+          <t>118166</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7800,12 +7800,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7820,12 +7820,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>83500</t>
+          <t>84203</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>112742</t>
+          <t>113962</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7835,12 +7835,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>179080</t>
+          <t>180013</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>221419</t>
+          <t>220800</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>23,18%</t>
         </is>
       </c>
     </row>
@@ -8015,12 +8015,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>48762</t>
+          <t>48973</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>68890</t>
+          <t>68801</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8030,12 +8030,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>28,88%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>40,8%</t>
+          <t>40,74%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8050,12 +8050,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>50592</t>
+          <t>49712</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>71679</t>
+          <t>71334</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8065,12 +8065,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>27,28%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>39,34%</t>
+          <t>39,15%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8085,12 +8085,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>104900</t>
+          <t>104930</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>135288</t>
+          <t>133996</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>29,89%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>38,53%</t>
+          <t>38,17%</t>
         </is>
       </c>
     </row>
@@ -8128,12 +8128,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>36119</t>
+          <t>35660</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>54557</t>
+          <t>53898</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8143,12 +8143,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>32,31%</t>
+          <t>31,92%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8163,12 +8163,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>45327</t>
+          <t>44493</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>65151</t>
+          <t>65079</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8178,12 +8178,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>35,75%</t>
+          <t>35,71%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8198,12 +8198,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>86433</t>
+          <t>86288</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>112742</t>
+          <t>112103</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>32,11%</t>
+          <t>31,93%</t>
         </is>
       </c>
     </row>
@@ -8241,12 +8241,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>10473</t>
+          <t>10782</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>22888</t>
+          <t>23168</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8256,12 +8256,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8276,12 +8276,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>18413</t>
+          <t>18300</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>33642</t>
+          <t>33717</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8291,12 +8291,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8311,12 +8311,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>32393</t>
+          <t>32916</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>53310</t>
+          <t>52207</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8326,12 +8326,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>14,87%</t>
         </is>
       </c>
     </row>
@@ -8354,12 +8354,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4008</t>
+          <t>4202</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14227</t>
+          <t>14232</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8369,7 +8369,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -8389,12 +8389,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1396</t>
+          <t>1378</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7834</t>
+          <t>7735</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8404,12 +8404,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8424,12 +8424,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6542</t>
+          <t>6744</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>17498</t>
+          <t>17683</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8439,12 +8439,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,04%</t>
         </is>
       </c>
     </row>
@@ -8467,12 +8467,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>33251</t>
+          <t>33393</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>52316</t>
+          <t>51949</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8482,12 +8482,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>30,76%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8502,12 +8502,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>30481</t>
+          <t>30387</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>48314</t>
+          <t>48848</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8517,12 +8517,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>26,81%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8537,12 +8537,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>67874</t>
+          <t>67127</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>93913</t>
+          <t>94769</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8552,12 +8552,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>26,99%</t>
         </is>
       </c>
     </row>
@@ -8697,12 +8697,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>197221</t>
+          <t>198697</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>236994</t>
+          <t>236519</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8712,12 +8712,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>28,65%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>34,1%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8732,12 +8732,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>208469</t>
+          <t>209137</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>250688</t>
+          <t>251510</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8747,12 +8747,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>34,11%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8767,12 +8767,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>420693</t>
+          <t>420442</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>476349</t>
+          <t>476569</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8782,12 +8782,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>33,29%</t>
+          <t>33,31%</t>
         </is>
       </c>
     </row>
@@ -8810,12 +8810,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>206087</t>
+          <t>207022</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>247265</t>
+          <t>247665</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8825,12 +8825,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>29,85%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>35,65%</t>
+          <t>35,71%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8845,12 +8845,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>223911</t>
+          <t>224556</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>267559</t>
+          <t>268805</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8860,12 +8860,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>30,46%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>36,29%</t>
+          <t>36,46%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8880,12 +8880,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>441092</t>
+          <t>443165</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>498702</t>
+          <t>502193</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8895,12 +8895,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>30,97%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>34,85%</t>
+          <t>35,1%</t>
         </is>
       </c>
     </row>
@@ -8923,12 +8923,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>53445</t>
+          <t>53748</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>78077</t>
+          <t>78897</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8938,12 +8938,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8958,12 +8958,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>72732</t>
+          <t>72783</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>102770</t>
+          <t>101918</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8973,12 +8973,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8993,12 +8993,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>134649</t>
+          <t>134000</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>171386</t>
+          <t>171541</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9008,12 +9008,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>11,99%</t>
         </is>
       </c>
     </row>
@@ -9036,12 +9036,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>17015</t>
+          <t>17200</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>32771</t>
+          <t>33760</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9071,12 +9071,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>19884</t>
+          <t>19602</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>37424</t>
+          <t>37389</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9086,12 +9086,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9106,12 +9106,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>40291</t>
+          <t>40627</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>64828</t>
+          <t>64682</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9121,12 +9121,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,52%</t>
         </is>
       </c>
     </row>
@@ -9149,12 +9149,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>142822</t>
+          <t>142533</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>178275</t>
+          <t>178356</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9184,12 +9184,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>131632</t>
+          <t>131401</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>166683</t>
+          <t>166543</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9199,12 +9199,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9219,12 +9219,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>282618</t>
+          <t>282595</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>334049</t>
+          <t>333341</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9239,7 +9239,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>23,3%</t>
         </is>
       </c>
     </row>
@@ -9610,12 +9610,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>338</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4849</t>
+          <t>4634</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9625,12 +9625,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>45,6%</t>
+          <t>43,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9645,12 +9645,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>525</t>
+          <t>545</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6792</t>
+          <t>6733</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9660,12 +9660,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>49,12%</t>
+          <t>48,69%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9680,12 +9680,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1879</t>
+          <t>1917</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9249</t>
+          <t>9494</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9695,12 +9695,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>37,81%</t>
+          <t>38,81%</t>
         </is>
       </c>
     </row>
@@ -9723,12 +9723,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3603</t>
+          <t>3738</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9564</t>
+          <t>9725</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9738,12 +9738,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33,88%</t>
+          <t>35,15%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,94%</t>
+          <t>91,46%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9758,12 +9758,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3351</t>
+          <t>3160</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9739</t>
+          <t>9514</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9773,12 +9773,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>70,42%</t>
+          <t>68,79%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9793,12 +9793,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>8334</t>
+          <t>8956</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>18690</t>
+          <t>18391</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9808,12 +9808,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>36,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>76,41%</t>
+          <t>75,18%</t>
         </is>
       </c>
     </row>
@@ -9841,7 +9841,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2514</t>
+          <t>2559</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9856,7 +9856,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>24,07%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9876,7 +9876,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5455</t>
+          <t>5457</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9891,7 +9891,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>39,45%</t>
+          <t>39,46%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9906,12 +9906,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>378</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>5635</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9921,12 +9921,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>23,04%</t>
         </is>
       </c>
     </row>
@@ -9954,7 +9954,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2279</t>
+          <t>2122</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -9969,7 +9969,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9989,7 +9989,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4693</t>
+          <t>4109</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10004,7 +10004,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,93%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4645</t>
+          <t>5255</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10039,7 +10039,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>21,48%</t>
         </is>
       </c>
     </row>
@@ -10067,7 +10067,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4136</t>
+          <t>4173</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10082,7 +10082,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>38,9%</t>
+          <t>39,25%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10097,12 +10097,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>540</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5193</t>
+          <t>5075</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>37,55%</t>
+          <t>36,7%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1144</t>
+          <t>1164</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>7090</t>
+          <t>6856</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>28,03%</t>
         </is>
       </c>
     </row>
@@ -10292,12 +10292,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18973</t>
+          <t>18961</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>33539</t>
+          <t>33413</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10307,12 +10307,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>21,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>38,04%</t>
+          <t>37,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10327,12 +10327,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>25902</t>
+          <t>26201</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>46536</t>
+          <t>45519</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10342,12 +10342,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,93%</t>
+          <t>34,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10362,12 +10362,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>50768</t>
+          <t>49960</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>74545</t>
+          <t>74953</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10377,12 +10377,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,67%</t>
+          <t>33,86%</t>
         </is>
       </c>
     </row>
@@ -10405,12 +10405,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>25478</t>
+          <t>25774</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>40319</t>
+          <t>40248</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10420,12 +10420,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>45,73%</t>
+          <t>45,65%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10440,12 +10440,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>48780</t>
+          <t>51288</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>73369</t>
+          <t>72933</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10455,12 +10455,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>36,62%</t>
+          <t>38,5%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>55,07%</t>
+          <t>54,75%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10475,12 +10475,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>81122</t>
+          <t>79986</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>107412</t>
+          <t>108397</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10490,12 +10490,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>36,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>48,52%</t>
+          <t>48,96%</t>
         </is>
       </c>
     </row>
@@ -10518,12 +10518,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6588</t>
+          <t>6359</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>17086</t>
+          <t>16341</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10533,12 +10533,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10553,12 +10553,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>12951</t>
+          <t>12949</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>27465</t>
+          <t>28035</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10573,7 +10573,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10588,12 +10588,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>22338</t>
+          <t>22648</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>38775</t>
+          <t>40726</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10603,12 +10603,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>18,4%</t>
         </is>
       </c>
     </row>
@@ -10631,12 +10631,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1875</t>
+          <t>1801</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8461</t>
+          <t>8491</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10646,12 +10646,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10666,12 +10666,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1724</t>
+          <t>1752</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9275</t>
+          <t>9633</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10681,12 +10681,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10701,12 +10701,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4781</t>
+          <t>4908</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14582</t>
+          <t>15108</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10716,12 +10716,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,82%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>9039</t>
+          <t>9110</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>20909</t>
+          <t>20936</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10759,12 +10759,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>7002</t>
+          <t>7087</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>19219</t>
+          <t>19247</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>18791</t>
+          <t>19128</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>36914</t>
+          <t>37145</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,78%</t>
         </is>
       </c>
     </row>
@@ -10974,12 +10974,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8829</t>
+          <t>9121</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19009</t>
+          <t>19101</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10989,12 +10989,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>43,95%</t>
+          <t>44,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11009,12 +11009,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7629</t>
+          <t>7809</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18192</t>
+          <t>17397</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11024,12 +11024,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>40,68%</t>
+          <t>38,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11044,12 +11044,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>19972</t>
+          <t>19240</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>33637</t>
+          <t>32952</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11059,12 +11059,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>37,46%</t>
         </is>
       </c>
     </row>
@@ -11087,12 +11087,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12794</t>
+          <t>12748</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>23072</t>
+          <t>22937</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11102,12 +11102,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>29,48%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>53,35%</t>
+          <t>53,04%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11122,12 +11122,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>16373</t>
+          <t>16282</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>27956</t>
+          <t>27753</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11137,12 +11137,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>36,61%</t>
+          <t>36,41%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>62,51%</t>
+          <t>62,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11157,12 +11157,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>31888</t>
+          <t>32058</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>47663</t>
+          <t>47634</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11172,12 +11172,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>36,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>54,18%</t>
+          <t>54,15%</t>
         </is>
       </c>
     </row>
@@ -11200,12 +11200,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4369</t>
+          <t>4481</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>12215</t>
+          <t>12553</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11215,12 +11215,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>29,02%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11235,12 +11235,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>870</t>
+          <t>1005</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8451</t>
+          <t>8475</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11270,12 +11270,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>6312</t>
+          <t>7087</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>16733</t>
+          <t>17294</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>19,66%</t>
         </is>
       </c>
     </row>
@@ -11313,12 +11313,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>710</t>
+          <t>723</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5763</t>
+          <t>6027</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11328,12 +11328,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11353,7 +11353,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5833</t>
+          <t>5481</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11368,7 +11368,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11383,12 +11383,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1525</t>
+          <t>1461</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8652</t>
+          <t>9113</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11398,12 +11398,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>10,36%</t>
         </is>
       </c>
     </row>
@@ -11426,12 +11426,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>626</t>
+          <t>627</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5444</t>
+          <t>5162</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11446,7 +11446,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11461,12 +11461,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1895</t>
+          <t>1944</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>10526</t>
+          <t>10745</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11476,12 +11476,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11496,12 +11496,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3495</t>
+          <t>3523</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>13851</t>
+          <t>13276</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11511,12 +11511,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>15,09%</t>
         </is>
       </c>
     </row>
@@ -11656,12 +11656,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>32918</t>
+          <t>33317</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>51454</t>
+          <t>52833</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11671,12 +11671,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>36,22%</t>
+          <t>37,19%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11691,12 +11691,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>39453</t>
+          <t>40833</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>61544</t>
+          <t>63218</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>32,09%</t>
+          <t>32,97%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>78612</t>
+          <t>78981</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>107942</t>
+          <t>107965</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11741,7 +11741,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -11769,12 +11769,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>47933</t>
+          <t>47381</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>67901</t>
+          <t>67057</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11784,12 +11784,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>33,35%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>47,8%</t>
+          <t>47,2%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11804,12 +11804,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>76884</t>
+          <t>76211</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>104283</t>
+          <t>103316</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>40,09%</t>
+          <t>39,74%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>54,38%</t>
+          <t>53,87%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>130084</t>
+          <t>130279</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>164376</t>
+          <t>164177</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>38,97%</t>
+          <t>39,03%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>49,24%</t>
+          <t>49,18%</t>
         </is>
       </c>
     </row>
@@ -11882,12 +11882,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>13515</t>
+          <t>13279</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>26508</t>
+          <t>26296</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11897,12 +11897,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11917,12 +11917,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>17758</t>
+          <t>17829</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>34728</t>
+          <t>33891</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11952,12 +11952,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>34186</t>
+          <t>34000</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>55141</t>
+          <t>55992</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,77%</t>
         </is>
       </c>
     </row>
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3481</t>
+          <t>3792</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>12109</t>
+          <t>12044</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12010,12 +12010,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12030,12 +12030,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3046</t>
+          <t>3366</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>12992</t>
+          <t>13595</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12045,12 +12045,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12065,12 +12065,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>8675</t>
+          <t>8844</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>21994</t>
+          <t>22411</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12080,12 +12080,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,71%</t>
         </is>
       </c>
     </row>
@@ -12108,12 +12108,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>11163</t>
+          <t>10979</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>24741</t>
+          <t>24588</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12123,12 +12123,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12143,12 +12143,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>13250</t>
+          <t>12543</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>29054</t>
+          <t>28293</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12158,12 +12158,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12178,12 +12178,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>26994</t>
+          <t>27444</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>47091</t>
+          <t>48316</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12193,12 +12193,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,47%</t>
         </is>
       </c>
     </row>
